--- a/annotated_data/mcmaster_reddit_part_2.xlsx
+++ b/annotated_data/mcmaster_reddit_part_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\大四\4NL3\4NL3_Final_Project_Step2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365-my.sharepoint.com/personal/guz38_mcmaster_ca/Documents/COMPSCI 4NL3/cs4nl-final-project/annotated_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEEA3DC-50E9-417A-A13C-6BC6CBB5BB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5FEEA3DC-50E9-417A-A13C-6BC6CBB5BB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{771CD39A-B277-4C71-BAEF-48372B35C505}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8050" yWindow="1660" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -1016,12 +1016,15 @@
     <t xml:space="preserve">Hi guys, did anyone take stats 4a03 itch P.E Jaguyo? Do you’ll have midterms or assignments from previous semester? previous Midterms would help me practice and get idea of how he tests. Thanks. </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>M</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1102,7 +1105,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1115,6 +1118,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1297,12 +1304,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C173"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="29">
       <c r="A2">
         <v>345</v>
       </c>
@@ -1324,7 +1331,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="58">
       <c r="A3">
         <v>346</v>
       </c>
@@ -1335,7 +1342,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="116">
       <c r="A4">
         <v>347</v>
       </c>
@@ -1346,7 +1353,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="29">
       <c r="A5">
         <v>348</v>
       </c>
@@ -1357,7 +1364,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="43.5">
       <c r="A6">
         <v>349</v>
       </c>
@@ -1368,15 +1375,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>350</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="43.5">
       <c r="A8">
         <v>351</v>
       </c>
@@ -1387,7 +1397,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>352</v>
       </c>
@@ -1398,7 +1408,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="74.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="74.5">
       <c r="A10">
         <v>353</v>
       </c>
@@ -1409,7 +1419,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="58">
       <c r="A11">
         <v>354</v>
       </c>
@@ -1420,7 +1430,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="409.5">
       <c r="A12">
         <v>355</v>
       </c>
@@ -1431,7 +1441,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="145">
       <c r="A13">
         <v>356</v>
       </c>
@@ -1442,7 +1452,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="101.5">
       <c r="A14">
         <v>357</v>
       </c>
@@ -1453,7 +1463,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="43.5">
       <c r="A15">
         <v>358</v>
       </c>
@@ -1464,7 +1474,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="58">
       <c r="A16">
         <v>359</v>
       </c>
@@ -1475,7 +1485,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="43.5">
       <c r="A17">
         <v>360</v>
       </c>
@@ -1486,7 +1496,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="72.5">
       <c r="A18">
         <v>361</v>
       </c>
@@ -1497,7 +1507,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="43.5">
       <c r="A19">
         <v>362</v>
       </c>
@@ -1508,7 +1518,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="101.5">
       <c r="A20">
         <v>363</v>
       </c>
@@ -1519,7 +1529,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="130.5">
       <c r="A21">
         <v>364</v>
       </c>
@@ -1530,7 +1540,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>365</v>
       </c>
@@ -1541,7 +1551,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="58">
       <c r="A23">
         <v>366</v>
       </c>
@@ -1552,7 +1562,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="72.5">
       <c r="A24">
         <v>367</v>
       </c>
@@ -1563,7 +1573,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="310.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" ht="325">
       <c r="A25">
         <v>368</v>
       </c>
@@ -1574,7 +1584,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" ht="72.5">
       <c r="A26">
         <v>369</v>
       </c>
@@ -1585,7 +1595,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" ht="116">
       <c r="A27">
         <v>370</v>
       </c>
@@ -1596,7 +1606,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" ht="29">
       <c r="A28">
         <v>371</v>
       </c>
@@ -1607,7 +1617,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>372</v>
       </c>
@@ -1618,7 +1628,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="29">
       <c r="A30">
         <v>373</v>
       </c>
@@ -1629,7 +1639,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" ht="87">
       <c r="A31">
         <v>374</v>
       </c>
@@ -1640,7 +1650,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" ht="58">
       <c r="A32">
         <v>375</v>
       </c>
@@ -1651,7 +1661,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="29">
       <c r="A33">
         <v>376</v>
       </c>
@@ -1662,7 +1672,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="29">
       <c r="A34">
         <v>377</v>
       </c>
@@ -1673,7 +1683,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="43.5">
       <c r="A35">
         <v>378</v>
       </c>
@@ -1684,7 +1694,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>379</v>
       </c>
@@ -1695,7 +1705,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" ht="145">
       <c r="A37">
         <v>380</v>
       </c>
@@ -1706,7 +1716,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="296" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" ht="310.5">
       <c r="A38">
         <v>381</v>
       </c>
@@ -1717,7 +1727,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="43.5">
       <c r="A39">
         <v>382</v>
       </c>
@@ -1728,7 +1738,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="130.5">
       <c r="A40">
         <v>383</v>
       </c>
@@ -1739,7 +1749,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>384</v>
       </c>
@@ -1750,7 +1760,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" ht="217.5">
       <c r="A42">
         <v>385</v>
       </c>
@@ -1761,7 +1771,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="72.5">
       <c r="A43">
         <v>386</v>
       </c>
@@ -1772,7 +1782,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="43.5">
       <c r="A44">
         <v>387</v>
       </c>
@@ -1783,7 +1793,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="31" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" ht="31">
       <c r="A45">
         <v>388</v>
       </c>
@@ -1794,7 +1804,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="377" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="377">
       <c r="A46">
         <v>389</v>
       </c>
@@ -1805,7 +1815,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>390</v>
       </c>
@@ -1816,7 +1826,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="203" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="203">
       <c r="A48">
         <v>391</v>
       </c>
@@ -1827,7 +1837,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="29">
       <c r="A49">
         <v>392</v>
       </c>
@@ -1838,7 +1848,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>393</v>
       </c>
@@ -1849,7 +1859,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" ht="87">
       <c r="A51">
         <v>394</v>
       </c>
@@ -1860,7 +1870,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" ht="43.5">
       <c r="A52">
         <v>395</v>
       </c>
@@ -1871,7 +1881,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" ht="58">
       <c r="A53">
         <v>396</v>
       </c>
@@ -1882,7 +1892,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" ht="43.5">
       <c r="A54">
         <v>397</v>
       </c>
@@ -1893,7 +1903,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="29">
       <c r="A55">
         <v>398</v>
       </c>
@@ -1904,7 +1914,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="174" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" ht="188.5">
       <c r="A56">
         <v>399</v>
       </c>
@@ -1915,7 +1925,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" ht="29">
       <c r="A57">
         <v>400</v>
       </c>
@@ -1926,7 +1936,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" ht="145">
       <c r="A58">
         <v>401</v>
       </c>
@@ -1937,7 +1947,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="89" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" ht="89">
       <c r="A59">
         <v>402</v>
       </c>
@@ -1948,7 +1958,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" ht="43.5">
       <c r="A60">
         <v>403</v>
       </c>
@@ -1959,7 +1969,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" ht="29">
       <c r="A61">
         <v>404</v>
       </c>
@@ -1970,7 +1980,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" ht="29">
       <c r="A62">
         <v>405</v>
       </c>
@@ -1981,7 +1991,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" ht="58">
       <c r="A63">
         <v>406</v>
       </c>
@@ -1992,7 +2002,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="180" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" ht="151">
       <c r="A64">
         <v>407</v>
       </c>
@@ -2003,7 +2013,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" ht="72.5">
       <c r="A65">
         <v>408</v>
       </c>
@@ -2014,7 +2024,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" ht="43.5">
       <c r="A66">
         <v>409</v>
       </c>
@@ -2025,7 +2035,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="174" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" ht="174">
       <c r="A67">
         <v>410</v>
       </c>
@@ -2036,7 +2046,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" ht="58">
       <c r="A68">
         <v>411</v>
       </c>
@@ -2047,7 +2057,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="29">
       <c r="A69">
         <v>412</v>
       </c>
@@ -2058,7 +2068,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>413</v>
       </c>
@@ -2069,7 +2079,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>414</v>
       </c>
@@ -2080,7 +2090,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="43.5">
       <c r="A72">
         <v>415</v>
       </c>
@@ -2091,7 +2101,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="29">
       <c r="A73">
         <v>416</v>
       </c>
@@ -2102,7 +2112,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" ht="16.5">
       <c r="A74">
         <v>417</v>
       </c>
@@ -2113,7 +2123,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="43.5">
       <c r="A75">
         <v>418</v>
       </c>
@@ -2124,7 +2134,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>419</v>
       </c>
@@ -2135,7 +2145,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="43.5">
       <c r="A77">
         <v>420</v>
       </c>
@@ -2146,7 +2156,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="58">
       <c r="A78">
         <v>421</v>
       </c>
@@ -2157,7 +2167,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>422</v>
       </c>
@@ -2168,7 +2178,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="29">
       <c r="A80">
         <v>423</v>
       </c>
@@ -2179,7 +2189,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="43.5">
       <c r="A81">
         <v>424</v>
       </c>
@@ -2190,7 +2200,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" ht="43.5">
       <c r="A82">
         <v>425</v>
       </c>
@@ -2201,7 +2211,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="87">
       <c r="A83">
         <v>426</v>
       </c>
@@ -2212,7 +2222,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="116">
       <c r="A84">
         <v>427</v>
       </c>
@@ -2223,7 +2233,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="406">
       <c r="A85">
         <v>428</v>
       </c>
@@ -2234,7 +2244,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="43.5">
       <c r="A86">
         <v>429</v>
       </c>
@@ -2245,7 +2255,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="29">
       <c r="A87">
         <v>430</v>
       </c>
@@ -2256,7 +2266,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>431</v>
       </c>
@@ -2267,7 +2277,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="319" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="319">
       <c r="A89">
         <v>432</v>
       </c>
@@ -2278,7 +2288,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>433</v>
       </c>
@@ -2289,7 +2299,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" ht="43.5">
       <c r="A91">
         <v>434</v>
       </c>
@@ -2300,7 +2310,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>435</v>
       </c>
@@ -2311,7 +2321,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="29">
       <c r="A93">
         <v>436</v>
       </c>
@@ -2322,7 +2332,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" ht="246.5">
       <c r="A94">
         <v>437</v>
       </c>
@@ -2333,7 +2343,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" ht="58">
       <c r="A95">
         <v>438</v>
       </c>
@@ -2344,7 +2354,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="362.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" ht="362.5">
       <c r="A96">
         <v>439</v>
       </c>
@@ -2355,7 +2365,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" ht="43.5">
       <c r="A97">
         <v>440</v>
       </c>
@@ -2366,7 +2376,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" ht="58">
       <c r="A98">
         <v>441</v>
       </c>
@@ -2377,7 +2387,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" ht="29">
       <c r="A99">
         <v>442</v>
       </c>
@@ -2388,7 +2398,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" ht="116">
       <c r="A100">
         <v>443</v>
       </c>
@@ -2399,7 +2409,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" ht="87">
       <c r="A101">
         <v>444</v>
       </c>
@@ -2410,7 +2420,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" ht="58">
       <c r="A102">
         <v>445</v>
       </c>
@@ -2421,7 +2431,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3">
       <c r="A103">
         <v>446</v>
       </c>
@@ -2432,7 +2442,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="29">
       <c r="A104">
         <v>447</v>
       </c>
@@ -2443,7 +2453,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" ht="159.5">
       <c r="A105">
         <v>448</v>
       </c>
@@ -2454,7 +2464,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" ht="43.5">
       <c r="A106">
         <v>449</v>
       </c>
@@ -2465,7 +2475,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" ht="29">
       <c r="A107">
         <v>450</v>
       </c>
@@ -2476,7 +2486,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" ht="72.5">
       <c r="A108">
         <v>451</v>
       </c>
@@ -2487,7 +2497,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" ht="29">
       <c r="A109">
         <v>452</v>
       </c>
@@ -2498,7 +2508,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" ht="58">
       <c r="A110">
         <v>453</v>
       </c>
@@ -2509,7 +2519,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="116">
       <c r="A111">
         <v>454</v>
       </c>
@@ -2520,7 +2530,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" ht="188.5">
       <c r="A112">
         <v>455</v>
       </c>
@@ -2531,7 +2541,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" ht="43.5">
       <c r="A113">
         <v>456</v>
       </c>
@@ -2542,7 +2552,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="72.5">
       <c r="A114">
         <v>457</v>
       </c>
@@ -2553,7 +2563,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" ht="29">
       <c r="A115">
         <v>458</v>
       </c>
@@ -2564,7 +2574,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" ht="29">
       <c r="A116">
         <v>459</v>
       </c>
@@ -2575,7 +2585,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" ht="43.5">
       <c r="A117">
         <v>460</v>
       </c>
@@ -2586,7 +2596,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" ht="58">
       <c r="A118">
         <v>461</v>
       </c>
@@ -2597,7 +2607,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" ht="58">
       <c r="A119">
         <v>462</v>
       </c>
@@ -2608,7 +2618,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" ht="116">
       <c r="A120">
         <v>463</v>
       </c>
@@ -2619,7 +2629,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="118" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" ht="118">
       <c r="A121">
         <v>464</v>
       </c>
@@ -2630,7 +2640,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3">
       <c r="A122">
         <v>465</v>
       </c>
@@ -2641,7 +2651,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" ht="116">
       <c r="A123">
         <v>466</v>
       </c>
@@ -2652,7 +2662,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" ht="43.5">
       <c r="A124">
         <v>467</v>
       </c>
@@ -2663,7 +2673,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3">
       <c r="A125">
         <v>468</v>
       </c>
@@ -2674,7 +2684,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" ht="29">
       <c r="A126">
         <v>469</v>
       </c>
@@ -2685,7 +2695,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" ht="72.5">
       <c r="A127">
         <v>470</v>
       </c>
@@ -2696,7 +2706,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="101.5">
       <c r="A128">
         <v>471</v>
       </c>
@@ -2707,7 +2717,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" ht="43.5">
       <c r="A129">
         <v>472</v>
       </c>
@@ -2718,7 +2728,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" ht="43.5">
       <c r="A130">
         <v>473</v>
       </c>
@@ -2729,7 +2739,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" ht="43.5">
       <c r="A131">
         <v>474</v>
       </c>
@@ -2740,7 +2750,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3">
       <c r="A132">
         <v>475</v>
       </c>
@@ -2751,7 +2761,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" ht="130.5">
       <c r="A133">
         <v>476</v>
       </c>
@@ -2762,7 +2772,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" ht="130.5">
       <c r="A134">
         <v>477</v>
       </c>
@@ -2773,7 +2783,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" ht="43.5">
       <c r="A135">
         <v>478</v>
       </c>
@@ -2784,7 +2794,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" ht="116">
       <c r="A136">
         <v>479</v>
       </c>
@@ -2795,7 +2805,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3">
       <c r="A137">
         <v>480</v>
       </c>
@@ -2806,7 +2816,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="290" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" ht="290">
       <c r="A138">
         <v>481</v>
       </c>
@@ -2817,7 +2827,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" ht="29">
       <c r="A139">
         <v>482</v>
       </c>
@@ -2828,7 +2838,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" ht="43.5">
       <c r="A140">
         <v>483</v>
       </c>
@@ -2839,7 +2849,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" ht="159.5">
       <c r="A141">
         <v>484</v>
       </c>
@@ -2850,7 +2860,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" ht="188.5">
       <c r="A142">
         <v>485</v>
       </c>
@@ -2861,7 +2871,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" ht="72.5">
       <c r="A143">
         <v>486</v>
       </c>
@@ -2872,7 +2882,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" ht="72.5">
       <c r="A144">
         <v>487</v>
       </c>
@@ -2883,7 +2893,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" ht="72.5">
       <c r="A145">
         <v>488</v>
       </c>
@@ -2894,7 +2904,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" ht="43.5">
       <c r="A146">
         <v>489</v>
       </c>
@@ -2905,7 +2915,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" ht="29">
       <c r="A147">
         <v>490</v>
       </c>
@@ -2916,7 +2926,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" ht="58">
       <c r="A148">
         <v>491</v>
       </c>
@@ -2927,7 +2937,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" ht="87">
       <c r="A149">
         <v>492</v>
       </c>
@@ -2938,7 +2948,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" ht="58">
       <c r="A150">
         <v>493</v>
       </c>
@@ -2949,7 +2959,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" ht="58">
       <c r="A151">
         <v>494</v>
       </c>
@@ -2960,7 +2970,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3">
       <c r="A152">
         <v>495</v>
       </c>
@@ -2971,7 +2981,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3">
       <c r="A153">
         <v>496</v>
       </c>
@@ -2982,7 +2992,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3">
       <c r="A154">
         <v>497</v>
       </c>
@@ -2993,7 +3003,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" ht="43.5">
       <c r="A155">
         <v>498</v>
       </c>
@@ -3004,7 +3014,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3">
       <c r="A156">
         <v>499</v>
       </c>
@@ -3015,7 +3025,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" ht="43.5">
       <c r="A157">
         <v>500</v>
       </c>
@@ -3026,7 +3036,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" ht="72.5">
       <c r="A158">
         <v>501</v>
       </c>
@@ -3037,7 +3047,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" ht="43.5">
       <c r="A159">
         <v>502</v>
       </c>
@@ -3048,7 +3058,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" ht="58">
       <c r="A160">
         <v>503</v>
       </c>
@@ -3059,7 +3069,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3">
       <c r="A161">
         <v>504</v>
       </c>
@@ -3070,7 +3080,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="174" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" ht="174">
       <c r="A162">
         <v>505</v>
       </c>
@@ -3081,7 +3091,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" ht="29">
       <c r="A163">
         <v>506</v>
       </c>
@@ -3092,15 +3102,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" ht="87">
       <c r="A164">
         <v>507</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C164" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
       <c r="A165">
         <v>508</v>
       </c>
@@ -3111,7 +3124,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" ht="58">
       <c r="A166">
         <v>509</v>
       </c>
@@ -3122,7 +3135,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" ht="29">
       <c r="A167">
         <v>510</v>
       </c>
@@ -3133,7 +3146,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" ht="29">
       <c r="A168">
         <v>511</v>
       </c>
@@ -3144,7 +3157,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3">
       <c r="A169">
         <v>512</v>
       </c>
@@ -3155,7 +3168,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3">
       <c r="A170">
         <v>513</v>
       </c>
@@ -3166,7 +3179,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" ht="29">
       <c r="A171">
         <v>514</v>
       </c>
@@ -3177,7 +3190,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="29">
       <c r="A172">
         <v>515</v>
       </c>
@@ -3188,7 +3201,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" ht="43.5">
       <c r="A173">
         <v>516</v>
       </c>
